--- a/Unified_PDF_Platform/unified_outputs/Aetna Bar louie (BLH) Feb-25 Inv_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/Aetna Bar louie (BLH) Feb-25 Inv_invoice.xlsx
@@ -2298,11 +2298,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>xxxxx0773</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2358,11 +2354,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>xxxxx1629</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2418,11 +2410,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>xxxxx8481</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2480,11 +2468,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>xxxxx5143</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2540,11 +2524,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>xxxxx7285</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2600,11 +2580,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>xxxxx0012</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2662,11 +2638,7 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>xxxxx4155</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2724,11 +2696,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>xxxxx7348</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2784,11 +2752,7 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>xxxxx4055</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2846,11 +2810,7 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>xxxxx7573</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2906,11 +2866,7 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>xxxxx8696</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -2966,11 +2922,7 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>xxxxx4455</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -3026,11 +2978,7 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>xxxxx9201</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -3088,7 +3036,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>xxxxx5134</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3148,7 +3096,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>xxxxx5116</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3210,7 +3158,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>xxxxx0730</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3272,7 +3220,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>xxxxx2365</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3332,7 +3280,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>xxxxx0919</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3392,7 +3340,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>xxxxx2924</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3452,7 +3400,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>xxxxx2556</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3514,7 +3462,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>xxxxx0276</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3522,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>xxxxx8470</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3584,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>xxxxx2155</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3646,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>xxxxx5845</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3758,7 +3706,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>xxxxx1214</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3776,7 +3724,7 @@
         <v>646.61</v>
       </c>
       <c r="O55" t="n">
-        <v>30.3</v>
+        <v>-616.3099999999999</v>
       </c>
       <c r="P55" t="inlineStr"/>
     </row>
@@ -3820,7 +3768,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>xxxxx7994</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3880,7 +3828,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>xxxxx2727</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5514,7 +5462,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>xxxxx0213</t>
+          <t>xxxx0213</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5574,7 +5522,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>xxxxx8171</t>
+          <t>xxxx8171</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5634,7 +5582,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>xxxxx1078</t>
+          <t>xxxx1078</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5696,7 +5644,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>xxxxx0792</t>
+          <t>xxxx0792</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5756,7 +5704,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>xxxxx3922</t>
+          <t>xxxx3922</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5816,7 +5764,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>xxxxx1258</t>
+          <t>xxxx1258</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5878,7 +5826,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>xxxxx4294</t>
+          <t>xxxx4294</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5940,7 +5888,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xxxxx5093</t>
+          <t>xxxx5093</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6000,7 +5948,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>xxxxx3607</t>
+          <t>xxxx3607</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6060,7 +6008,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>xxxxx8439</t>
+          <t>xxxx8439</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6122,7 +6070,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>xxxxx4990</t>
+          <t>xxxx4990</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6184,7 +6132,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>xxxxx8936</t>
+          <t>xxxx8936</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6246,7 +6194,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>xxxxx9136</t>
+          <t>xxxx9136</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6304,11 +6252,7 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>7903</t>
-        </is>
-      </c>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6364,11 +6308,7 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>2160</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6424,11 +6364,7 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>7449</t>
-        </is>
-      </c>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6484,11 +6420,7 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>3542</t>
-        </is>
-      </c>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6544,11 +6476,7 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>5707</t>
-        </is>
-      </c>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6604,11 +6532,7 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>8858</t>
-        </is>
-      </c>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6664,11 +6588,7 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>2387</t>
-        </is>
-      </c>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6726,11 +6646,7 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>6835</t>
-        </is>
-      </c>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6788,11 +6704,7 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>7430</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6850,11 +6762,7 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>4842</t>
-        </is>
-      </c>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6910,11 +6818,7 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>6445</t>
-        </is>
-      </c>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -6972,11 +6876,7 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>4878</t>
-        </is>
-      </c>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -7032,11 +6932,7 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>3169</t>
-        </is>
-      </c>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -7092,11 +6988,7 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -7152,11 +7044,7 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>6288</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -7214,7 +7102,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7274,7 +7162,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7336,7 +7224,7 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7396,7 +7284,7 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7456,7 +7344,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7516,7 +7404,7 @@
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7578,7 +7466,7 @@
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7638,7 +7526,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7698,7 +7586,7 @@
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7758,7 +7646,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7818,7 +7706,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7878,7 +7766,7 @@
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7938,7 +7826,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7998,7 +7886,7 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
-          <t>0023</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8056,11 +7944,7 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>xxxxxx3842</t>
-        </is>
-      </c>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8116,11 +8000,7 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>xxxxxx3621</t>
-        </is>
-      </c>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8176,11 +8056,7 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>xxxxxx8804</t>
-        </is>
-      </c>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8236,11 +8112,7 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>xxxxxx3706</t>
-        </is>
-      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8296,11 +8168,7 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>xxxxxx8179</t>
-        </is>
-      </c>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8358,11 +8226,7 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>xxxxxx3504</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8418,11 +8282,7 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>xxxxxx6467</t>
-        </is>
-      </c>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8478,11 +8338,7 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>xxxxxx4004</t>
-        </is>
-      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8538,11 +8394,7 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>xxxxxx7423</t>
-        </is>
-      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8598,11 +8450,7 @@
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>xxxxxx2223</t>
-        </is>
-      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8660,11 +8508,7 @@
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>xxxxxx7970</t>
-        </is>
-      </c>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8720,11 +8564,7 @@
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>xxxxxx8662</t>
-        </is>
-      </c>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8780,11 +8620,7 @@
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>xxxxxx1787</t>
-        </is>
-      </c>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8842,11 +8678,7 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>xxxxxx4282</t>
-        </is>
-      </c>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8902,11 +8734,7 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>xxxxxx3688</t>
-        </is>
-      </c>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>Medical</t>
@@ -8964,7 +8792,7 @@
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
-          <t>0513</t>
+          <t>0023</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9026,7 +8854,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9086,7 +8914,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9146,7 +8974,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9206,7 +9034,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9266,7 +9094,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9326,7 +9154,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -9386,7 +9214,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9446,11 +9274,7 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
@@ -9506,11 +9330,7 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
@@ -9566,11 +9386,7 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
@@ -9626,11 +9442,7 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
@@ -9782,11 +9594,7 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>xxxxx0403</t>
-        </is>
-      </c>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
@@ -9834,11 +9642,7 @@
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>xxxxx9341</t>
-        </is>
-      </c>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
@@ -9886,11 +9690,7 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>xxxxx8463</t>
-        </is>
-      </c>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
@@ -10097,25 +9897,13 @@
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>INVOICE TOTAL</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="n">

--- a/Unified_PDF_Platform/unified_outputs/Aetna Bar louie (BLH) Feb-25 Inv_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/Aetna Bar louie (BLH) Feb-25 Inv_invoice.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P162"/>
+  <dimension ref="A1:O165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,11 +504,6 @@
           <t>ADJUSTMENT_PREMIUM</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>PRICING_ADJUSTMENT</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -528,7 +523,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,27 +543,26 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N2" t="n">
         <v>745.01</v>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,7 +582,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,27 +602,26 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>1638.94</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,7 +641,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,27 +661,26 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>1638.94</v>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,7 +700,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -728,27 +720,26 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N5" t="n">
         <v>745.01</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,7 +759,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -788,27 +779,26 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N6" t="n">
         <v>745.01</v>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -828,7 +818,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,27 +838,26 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N7" t="n">
         <v>745.01</v>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -888,7 +877,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -908,27 +897,26 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N8" t="n">
         <v>745.01</v>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -948,7 +936,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -968,20 +956,20 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -990,7 +978,6 @@
       <c r="O9" t="n">
         <v>-893.9299999999999</v>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1010,7 +997,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1030,27 +1017,26 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N10" t="n">
         <v>745.01</v>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1070,7 +1056,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1090,27 +1076,26 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>745.01</v>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1130,7 +1115,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1150,27 +1135,26 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N12" t="n">
         <v>745.01</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1190,7 +1174,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,27 +1194,26 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>745.01</v>
       </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1250,7 +1233,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1270,27 +1253,26 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>745.01</v>
       </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1310,7 +1292,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1330,27 +1312,26 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N15" t="n">
         <v>745.01</v>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1370,7 +1351,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1390,27 +1371,26 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1600OAMCH.S.A</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N16" t="n">
         <v>745.01</v>
       </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1430,7 +1410,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1452,25 +1432,24 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>xxxxx1039</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>745.01</v>
       </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1490,7 +1469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1512,18 +1491,18 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>xxxxx7171</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1532,7 +1511,6 @@
       <c r="O18" t="n">
         <v>1638.94</v>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1552,7 +1530,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1574,25 +1552,24 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>xxxxx8636</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>745.01</v>
       </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1612,7 +1589,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1634,25 +1611,24 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>xxxxx8015</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N20" t="n">
         <v>745.01</v>
       </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1672,7 +1648,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1694,25 +1670,24 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>xxxxx3057</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>745.01</v>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1732,7 +1707,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1754,18 +1729,18 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>xxxxx5495</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -1774,7 +1749,6 @@
       <c r="O22" t="n">
         <v>2309.44</v>
       </c>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1794,7 +1768,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1816,25 +1790,24 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>xxxxx9979</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N23" t="n">
         <v>745.01</v>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1854,7 +1827,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1876,18 +1849,18 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>xxxxx0202</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -1896,7 +1869,6 @@
       <c r="O24" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1916,7 +1888,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1938,25 +1910,24 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>xxxxx0727</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N25" t="n">
         <v>745.01</v>
       </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1976,7 +1947,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1998,18 +1969,18 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>xxxxx6035</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -2018,7 +1989,6 @@
       <c r="O26" t="n">
         <v>208.26</v>
       </c>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2038,7 +2008,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2060,25 +2030,24 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>xxxxx6366</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N27" t="n">
         <v>745.01</v>
       </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2098,7 +2067,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2120,25 +2089,24 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>xxxxx9342</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N28" t="n">
         <v>745.01</v>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2158,7 +2126,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2180,25 +2148,24 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>xxxxx2285</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N29" t="n">
         <v>745.01</v>
       </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2218,7 +2185,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2240,25 +2207,24 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>xxxxx7992</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N30" t="n">
         <v>745.01</v>
       </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2278,7 +2244,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2304,17 +2270,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N31" t="n">
         <v>745.01</v>
       </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2334,7 +2303,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2360,17 +2329,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N32" t="n">
         <v>745.01</v>
       </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2390,7 +2362,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2416,10 +2388,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -2428,7 +2404,6 @@
       <c r="O33" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2448,7 +2423,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2474,17 +2449,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N34" t="n">
         <v>745.01</v>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2504,7 +2482,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2530,17 +2508,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N35" t="n">
         <v>745.01</v>
       </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2560,7 +2541,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2586,10 +2567,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -2598,7 +2583,6 @@
       <c r="O36" t="n">
         <v>646.61</v>
       </c>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2618,7 +2602,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2644,10 +2628,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -2656,7 +2644,6 @@
       <c r="O37" t="n">
         <v>646.61</v>
       </c>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2676,7 +2663,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2702,17 +2689,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N38" t="n">
         <v>646.61</v>
       </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2732,7 +2722,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2758,10 +2748,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -2770,7 +2764,6 @@
       <c r="O39" t="n">
         <v>646.61</v>
       </c>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2790,7 +2783,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2816,17 +2809,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N40" t="n">
         <v>646.61</v>
       </c>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2846,7 +2842,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2872,17 +2868,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N41" t="n">
         <v>646.61</v>
       </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2902,7 +2901,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2928,17 +2927,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N42" t="n">
         <v>646.61</v>
       </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2958,7 +2960,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2984,17 +2986,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N43" t="n">
         <v>646.61</v>
       </c>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3014,7 +3019,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3034,27 +3039,26 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N44" t="n">
         <v>1228.53</v>
       </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3074,7 +3078,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3094,20 +3098,20 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -3116,7 +3120,6 @@
       <c r="O45" t="n">
         <v>646.61</v>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3136,7 +3139,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3156,20 +3159,20 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -3178,7 +3181,6 @@
       <c r="O46" t="n">
         <v>646.61</v>
       </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3198,7 +3200,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3218,27 +3220,26 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N47" t="n">
         <v>646.61</v>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3258,7 +3259,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3278,27 +3279,26 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N48" t="n">
         <v>646.61</v>
       </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3338,27 +3338,26 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N49" t="n">
         <v>646.61</v>
       </c>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3378,7 +3377,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3398,20 +3397,20 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -3420,7 +3419,6 @@
       <c r="O50" t="n">
         <v>1422.53</v>
       </c>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3440,7 +3438,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3460,27 +3458,26 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N51" t="n">
         <v>2004.44</v>
       </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3500,7 +3497,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3520,20 +3517,20 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -3542,7 +3539,6 @@
       <c r="O52" t="n">
         <v>-186.93</v>
       </c>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3562,7 +3558,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3582,20 +3578,20 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -3604,7 +3600,6 @@
       <c r="O53" t="n">
         <v>646.61</v>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3624,7 +3619,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3644,27 +3639,26 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>646.61</v>
       </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3684,7 +3678,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3704,20 +3698,20 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -3726,7 +3720,6 @@
       <c r="O55" t="n">
         <v>-616.3099999999999</v>
       </c>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3746,7 +3739,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3766,27 +3759,26 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N56" t="n">
         <v>646.61</v>
       </c>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3806,7 +3798,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3826,27 +3818,26 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N57" t="n">
         <v>646.61</v>
       </c>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3866,7 +3857,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3886,27 +3877,26 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>2500OAMCHSA</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N58" t="n">
         <v>646.61</v>
       </c>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3926,7 +3916,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3946,20 +3936,20 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -3968,7 +3958,6 @@
       <c r="O59" t="n">
         <v>450.9</v>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3988,7 +3977,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4008,27 +3997,26 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N60" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4048,7 +4036,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4068,27 +4056,26 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N61" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4108,7 +4095,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4128,27 +4115,26 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N62" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4168,7 +4154,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4188,27 +4174,26 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N63" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4228,7 +4213,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4248,27 +4233,26 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N64" t="n">
         <v>1355.84</v>
       </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4288,7 +4272,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4308,20 +4292,20 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -4330,7 +4314,6 @@
       <c r="O65" t="n">
         <v>616.3099999999999</v>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4350,7 +4333,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4370,27 +4353,26 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N66" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4410,7 +4392,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4430,27 +4412,26 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N67" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4470,7 +4451,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4490,27 +4471,26 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N68" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4530,7 +4510,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4550,20 +4530,20 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>4500OAMCH.S.A</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -4572,7 +4552,6 @@
       <c r="O69" t="n">
         <v>616.3099999999999</v>
       </c>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4592,7 +4571,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4612,27 +4591,22 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N70" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4652,7 +4626,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4672,27 +4646,22 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N71" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4712,7 +4681,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4732,27 +4701,22 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N72" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4772,7 +4736,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4792,20 +4756,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -4814,7 +4774,6 @@
       <c r="O73" t="n">
         <v>616.3099999999999</v>
       </c>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4834,7 +4793,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4854,27 +4813,22 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N74" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4894,7 +4848,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4914,20 +4868,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -4936,7 +4886,6 @@
       <c r="O75" t="n">
         <v>-57.54</v>
       </c>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4956,7 +4905,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4976,20 +4925,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -4998,7 +4943,6 @@
       <c r="O76" t="n">
         <v>1355.84</v>
       </c>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5018,7 +4962,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5038,27 +4982,22 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N77" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5078,7 +5017,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5098,27 +5037,22 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N78" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5138,7 +5072,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5158,20 +5092,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -5180,7 +5110,6 @@
       <c r="O79" t="n">
         <v>-128.7</v>
       </c>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5200,7 +5129,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5220,27 +5149,22 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N80" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5260,7 +5184,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5280,27 +5204,22 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N81" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5320,7 +5239,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5340,27 +5259,22 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N82" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5380,7 +5294,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5400,27 +5314,22 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N83" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5440,7 +5349,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5462,7 +5371,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>xxxx0213</t>
+          <t>0213</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5470,17 +5379,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N84" t="n">
         <v>1873.43</v>
       </c>
       <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5500,7 +5412,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5522,7 +5434,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>xxxx8171</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5530,17 +5442,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N85" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5560,7 +5475,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5582,7 +5497,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>xxxx1078</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5590,10 +5505,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -5602,7 +5521,6 @@
       <c r="O86" t="n">
         <v>616.3099999999999</v>
       </c>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5622,7 +5540,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5644,7 +5562,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>xxxx0792</t>
+          <t>0792</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5652,17 +5570,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N87" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5682,7 +5603,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5704,7 +5625,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>xxxx3922</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5712,17 +5633,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N88" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5742,7 +5666,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5764,7 +5688,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>xxxx1258</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5772,10 +5696,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -5784,7 +5712,6 @@
       <c r="O89" t="n">
         <v>536.75</v>
       </c>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5804,7 +5731,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5826,7 +5753,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>xxxx4294</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5834,10 +5761,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -5846,7 +5777,6 @@
       <c r="O90" t="n">
         <v>536.75</v>
       </c>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5866,7 +5796,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5888,7 +5818,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>xxxx5093</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5896,17 +5826,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N91" t="n">
         <v>536.75</v>
       </c>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5926,7 +5859,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5948,7 +5881,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>xxxx3607</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5956,17 +5889,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N92" t="n">
         <v>536.75</v>
       </c>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5986,7 +5922,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6008,7 +5944,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>xxxx8439</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6016,10 +5952,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -6028,7 +5968,6 @@
       <c r="O93" t="n">
         <v>536.75</v>
       </c>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6048,7 +5987,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6070,7 +6009,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>xxxx4990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6078,10 +6017,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -6090,7 +6033,6 @@
       <c r="O94" t="n">
         <v>-109.86</v>
       </c>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6110,7 +6052,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6132,7 +6074,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>xxxx8936</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6140,10 +6082,14 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -6152,7 +6098,6 @@
       <c r="O95" t="n">
         <v>536.75</v>
       </c>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6172,7 +6117,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6194,7 +6139,7 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
-          <t>xxxx9136</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6202,17 +6147,20 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N96" t="n">
         <v>536.75</v>
       </c>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6232,7 +6180,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6253,22 +6201,21 @@
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>FAM</t>
         </is>
       </c>
       <c r="N97" t="n">
         <v>1422.53</v>
       </c>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6288,7 +6235,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6309,22 +6256,21 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N98" t="n">
         <v>536.75</v>
       </c>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6344,7 +6290,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6365,22 +6311,21 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N99" t="n">
         <v>536.75</v>
       </c>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6400,7 +6345,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6421,22 +6366,21 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N100" t="n">
         <v>536.75</v>
       </c>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6456,7 +6400,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6477,22 +6421,21 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N101" t="n">
         <v>536.75</v>
       </c>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6512,7 +6455,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6533,22 +6476,21 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N102" t="n">
         <v>536.75</v>
       </c>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6568,7 +6510,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6589,15 +6531,15 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N103" t="n">
@@ -6606,7 +6548,6 @@
       <c r="O103" t="n">
         <v>536.75</v>
       </c>
-      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6626,7 +6567,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6647,15 +6588,15 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -6664,7 +6605,6 @@
       <c r="O104" t="n">
         <v>-59.62</v>
       </c>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6684,7 +6624,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6705,15 +6645,15 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -6722,7 +6662,6 @@
       <c r="O105" t="n">
         <v>536.75</v>
       </c>
-      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6742,7 +6681,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6763,22 +6702,21 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N106" t="n">
         <v>536.75</v>
       </c>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6798,7 +6736,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6819,15 +6757,15 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -6836,7 +6774,6 @@
       <c r="O107" t="n">
         <v>536.75</v>
       </c>
-      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6856,7 +6793,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6877,22 +6814,21 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N108" t="n">
         <v>536.75</v>
       </c>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6912,7 +6848,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6933,22 +6869,21 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="N109" t="n">
         <v>1355.84</v>
       </c>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6968,7 +6903,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6989,22 +6924,21 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N110" t="n">
         <v>536.75</v>
       </c>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7024,7 +6958,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7045,22 +6979,21 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Medical</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N111" t="n">
         <v>536.75</v>
       </c>
       <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7080,7 +7013,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7100,27 +7033,26 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N112" t="n">
         <v>536.75</v>
       </c>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7140,7 +7072,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7160,20 +7092,20 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -7182,7 +7114,6 @@
       <c r="O113" t="n">
         <v>536.75</v>
       </c>
-      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7202,7 +7133,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7222,27 +7153,26 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N114" t="n">
         <v>536.75</v>
       </c>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7262,7 +7192,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7282,27 +7212,26 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N115" t="n">
         <v>536.75</v>
       </c>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7322,7 +7251,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7342,27 +7271,26 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N116" t="n">
         <v>536.75</v>
       </c>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7382,7 +7310,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7402,20 +7330,20 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -7424,7 +7352,6 @@
       <c r="O117" t="n">
         <v>-208.26</v>
       </c>
-      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7444,7 +7371,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7464,27 +7391,26 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N118" t="n">
         <v>536.75</v>
       </c>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7504,7 +7430,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7524,27 +7450,26 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N119" t="n">
         <v>536.75</v>
       </c>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7564,7 +7489,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7584,27 +7509,26 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N120" t="n">
         <v>1180.85</v>
       </c>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7624,7 +7548,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7644,27 +7568,26 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N121" t="n">
         <v>1180.85</v>
       </c>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7684,7 +7607,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7704,27 +7627,26 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N122" t="n">
         <v>536.75</v>
       </c>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7744,7 +7666,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7764,27 +7686,26 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N123" t="n">
         <v>536.75</v>
       </c>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7804,7 +7725,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7824,27 +7745,26 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N124" t="n">
         <v>536.75</v>
       </c>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7864,7 +7784,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7884,27 +7804,26 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>0106</t>
-        </is>
-      </c>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>Medical</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N125" t="n">
         <v>536.75</v>
       </c>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7924,7 +7843,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7950,17 +7869,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="n">
         <v>1180.85</v>
       </c>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7980,7 +7898,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8006,17 +7924,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
         <v>1422.53</v>
       </c>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8036,7 +7953,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8062,17 +7979,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
         <v>536.75</v>
       </c>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8092,7 +8008,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8118,17 +8034,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
         <v>1355.84</v>
       </c>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8148,7 +8063,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8174,19 +8089,18 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
         <v>536.75</v>
       </c>
       <c r="O130" t="n">
         <v>536.75</v>
       </c>
-      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8206,7 +8120,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8232,17 +8146,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
         <v>536.75</v>
       </c>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8262,7 +8175,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8288,17 +8201,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
         <v>536.75</v>
       </c>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8318,7 +8230,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8344,17 +8256,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>1180.85</v>
       </c>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8374,7 +8285,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8400,17 +8311,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
         <v>536.75</v>
       </c>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8430,7 +8340,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8456,19 +8366,18 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
         <v>1422.53</v>
       </c>
       <c r="O135" t="n">
         <v>1422.53</v>
       </c>
-      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8488,7 +8397,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8514,17 +8423,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
         <v>536.75</v>
       </c>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8544,7 +8452,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8570,17 +8478,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
         <v>1355.84</v>
       </c>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8600,7 +8507,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8626,19 +8533,18 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="n">
         <v>536.75</v>
       </c>
       <c r="O138" t="n">
         <v>536.75</v>
       </c>
-      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8658,7 +8564,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8684,17 +8590,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
         <v>536.75</v>
       </c>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8714,7 +8619,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8740,17 +8645,16 @@
           <t>Medical</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
         <v>1422.53</v>
       </c>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8770,7 +8674,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8790,20 +8694,20 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>0023</t>
-        </is>
-      </c>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>5000SJOAMCACTIVE</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N141" t="n">
@@ -8812,7 +8716,6 @@
       <c r="O141" t="n">
         <v>536.75</v>
       </c>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8832,7 +8735,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8852,27 +8755,26 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>1600PPOH.S.AACTIVE</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N142" t="n">
         <v>745.01</v>
       </c>
       <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8892,7 +8794,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8912,27 +8814,26 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>1600PPOH.S.AACTIVE</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N143" t="n">
         <v>745.01</v>
       </c>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8952,7 +8853,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8972,27 +8873,26 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>1600PPOH.S.AACTIVE</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N144" t="n">
         <v>745.01</v>
       </c>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9012,7 +8912,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9032,27 +8932,26 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>2500PPOH.S.AACTIVE</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N145" t="n">
         <v>646.61</v>
       </c>
       <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9072,7 +8971,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9092,27 +8991,26 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>4500PPOH.S.AACTIVE</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N146" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9132,7 +9030,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9152,27 +9050,26 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>4500PPOH.S.AACTIVE</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N147" t="n">
         <v>616.3099999999999</v>
       </c>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9192,7 +9089,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9212,20 +9109,20 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>0024</t>
-        </is>
-      </c>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="N148" t="n">
@@ -9234,7 +9131,6 @@
       <c r="O148" t="n">
         <v>-241.68</v>
       </c>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9254,7 +9150,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9274,23 +9170,30 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>xxxxx0645</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N149" t="n">
         <v>536.75</v>
       </c>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9310,7 +9213,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9330,23 +9233,30 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>xxxxx6310</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N150" t="n">
         <v>536.75</v>
       </c>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9366,7 +9276,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9386,23 +9296,30 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>xxxxx1512</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N151" t="n">
         <v>536.75</v>
       </c>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9422,7 +9339,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9442,23 +9359,30 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>xxxxx7770</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr">
         <is>
           <t>5000SJPPOACTIVE</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>MEDICAL</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="N152" t="n">
         <v>536.75</v>
       </c>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9478,7 +9402,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9506,7 +9430,6 @@
       <c r="O153" t="n">
         <v>1415.46</v>
       </c>
-      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9526,7 +9449,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9554,7 +9477,6 @@
       <c r="O154" t="n">
         <v>745.01</v>
       </c>
-      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9574,7 +9496,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9602,7 +9524,6 @@
       <c r="O155" t="n">
         <v>-1032.31</v>
       </c>
-      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9622,7 +9543,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9650,7 +9571,6 @@
       <c r="O156" t="n">
         <v>-646.61</v>
       </c>
-      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9670,7 +9590,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9698,7 +9618,6 @@
       <c r="O157" t="n">
         <v>-616.3099999999999</v>
       </c>
-      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9718,7 +9637,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9746,7 +9665,6 @@
       <c r="O158" t="n">
         <v>-616.3099999999999</v>
       </c>
-      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9766,7 +9684,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9794,7 +9712,6 @@
       <c r="O159" t="n">
         <v>-536.75</v>
       </c>
-      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9814,7 +9731,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9842,7 +9759,6 @@
       <c r="O160" t="n">
         <v>-1180.85</v>
       </c>
-      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9862,7 +9778,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>02/01/25-02/28/25</t>
+          <t>02/01/25</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9890,7 +9806,6 @@
       <c r="O161" t="n">
         <v>-536.75</v>
       </c>
-      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -9903,14 +9818,86 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>TOTAL CURRENT PREMIUM</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="n">
+        <v>116069.1999999999</v>
+      </c>
+      <c r="O162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>TOTAL ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="n">
+        <v>15746.13999999998</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (COMBINED)</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="n">
+        <v>131815.3399999999</v>
+      </c>
+      <c r="O164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>REPORTED INVOICE TOTAL (FOR AUDIT)</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="n">
         <v>116069.2</v>
       </c>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
